--- a/基础竞品分析工具/竞品分析基本测试项模板.xlsx
+++ b/基础竞品分析工具/竞品分析基本测试项模板.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PythonProject2\基础竞品分析自己修改 - 0115修改功能\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PythonProject\基础竞品分析工具\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -139,13 +139,7 @@
     <t>Write</t>
   </si>
   <si>
-    <t>TLC顺序</t>
-  </si>
-  <si>
     <t>TLC+GC</t>
-  </si>
-  <si>
-    <t>TLC+GC顺序</t>
   </si>
   <si>
     <t>高温</t>
@@ -207,7 +201,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FILL CARD顺序</t>
+    <t>TLC顺序写</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TLC+GC顺序写</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FILL CARD顺序写</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -925,47 +927,53 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -973,14 +981,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1044,7 +1046,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1617,7 +1618,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1665,7 +1665,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11170,31 +11169,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15.65" customHeight="1">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="79" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="82" t="s">
+      <c r="C1" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="82" t="s">
+      <c r="E1" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="75" t="s">
+      <c r="H1" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="75" t="s">
+      <c r="I1" s="77" t="s">
         <v>19</v>
       </c>
       <c r="L1" s="3"/>
@@ -11226,31 +11225,31 @@
       <c r="X2" s="4"/>
     </row>
     <row r="3" spans="1:24" ht="15.65" customHeight="1">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="77" t="s">
+      <c r="C3" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="77" t="s">
+      <c r="D3" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="77" t="s">
+      <c r="E3" s="75" t="s">
         <v>23</v>
       </c>
       <c r="F3" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="87" t="s">
+      <c r="G3" s="80" t="s">
         <v>25</v>
       </c>
       <c r="H3" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="83" t="s">
+      <c r="I3" s="87" t="s">
         <v>27</v>
       </c>
       <c r="J3" s="64"/>
@@ -11282,7 +11281,7 @@
       <c r="H4" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="80"/>
+      <c r="I4" s="82"/>
       <c r="J4" s="64"/>
       <c r="K4" s="64"/>
       <c r="L4" s="64"/>
@@ -11312,7 +11311,7 @@
       <c r="H5" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="80"/>
+      <c r="I5" s="82"/>
       <c r="J5" s="64"/>
       <c r="K5" s="64"/>
       <c r="L5" s="64"/>
@@ -11342,7 +11341,7 @@
       <c r="H6" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="80"/>
+      <c r="I6" s="82"/>
       <c r="J6" s="59"/>
       <c r="K6" s="59"/>
       <c r="L6" s="59"/>
@@ -11372,7 +11371,7 @@
       <c r="H7" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="81"/>
+      <c r="I7" s="83"/>
       <c r="J7" s="59"/>
       <c r="K7" s="59"/>
       <c r="L7" s="59"/>
@@ -11394,7 +11393,7 @@
       <c r="B8" s="78"/>
       <c r="C8" s="78"/>
       <c r="D8" s="78"/>
-      <c r="E8" s="77" t="s">
+      <c r="E8" s="75" t="s">
         <v>32</v>
       </c>
       <c r="F8" s="58" t="s">
@@ -11404,7 +11403,7 @@
       <c r="H8" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="79" t="s">
+      <c r="I8" s="86" t="s">
         <v>33</v>
       </c>
       <c r="J8" s="59"/>
@@ -11436,7 +11435,7 @@
       <c r="H9" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="80"/>
+      <c r="I9" s="82"/>
       <c r="J9" s="59"/>
       <c r="K9" s="59"/>
       <c r="L9" s="59"/>
@@ -11466,7 +11465,7 @@
       <c r="H10" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="80"/>
+      <c r="I10" s="82"/>
       <c r="J10" s="59"/>
       <c r="K10" s="59"/>
       <c r="L10" s="59"/>
@@ -11496,7 +11495,7 @@
       <c r="H11" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I11" s="80"/>
+      <c r="I11" s="82"/>
       <c r="J11" s="59"/>
       <c r="K11" s="59"/>
       <c r="L11" s="59"/>
@@ -11526,7 +11525,7 @@
       <c r="H12" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I12" s="81"/>
+      <c r="I12" s="83"/>
       <c r="J12" s="59"/>
       <c r="K12" s="59"/>
       <c r="L12" s="59"/>
@@ -11547,20 +11546,20 @@
       <c r="A13" s="78"/>
       <c r="B13" s="78"/>
       <c r="C13" s="78"/>
-      <c r="D13" s="77" t="s">
+      <c r="D13" s="75" t="s">
         <v>34</v>
       </c>
       <c r="E13" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="F13" s="77" t="s">
+      <c r="F13" s="75" t="s">
         <v>24</v>
       </c>
       <c r="G13" s="78"/>
       <c r="H13" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I13" s="86" t="s">
+      <c r="I13" s="85" t="s">
         <v>35</v>
       </c>
       <c r="J13" s="59"/>
@@ -11592,7 +11591,7 @@
       <c r="H14" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I14" s="81"/>
+      <c r="I14" s="83"/>
       <c r="J14" s="59"/>
       <c r="K14" s="59"/>
       <c r="L14" s="59"/>
@@ -11612,13 +11611,13 @@
     <row r="15" spans="1:24" ht="15.65" customHeight="1">
       <c r="A15" s="78"/>
       <c r="B15" s="78"/>
-      <c r="C15" s="87" t="s">
+      <c r="C15" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="77" t="s">
+      <c r="D15" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="85" t="s">
+      <c r="E15" s="84" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="58" t="s">
@@ -11628,8 +11627,8 @@
       <c r="H15" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I15" s="86" t="s">
-        <v>52</v>
+      <c r="I15" s="85" t="s">
+        <v>50</v>
       </c>
       <c r="J15" s="59"/>
       <c r="K15" s="59"/>
@@ -11660,7 +11659,7 @@
       <c r="H16" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="80"/>
+      <c r="I16" s="82"/>
       <c r="J16" s="59"/>
       <c r="K16" s="59"/>
       <c r="L16" s="59"/>
@@ -11690,7 +11689,7 @@
       <c r="H17" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="80"/>
+      <c r="I17" s="82"/>
       <c r="J17" s="59"/>
       <c r="K17" s="59"/>
       <c r="L17" s="59"/>
@@ -11720,7 +11719,7 @@
       <c r="H18" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I18" s="80"/>
+      <c r="I18" s="82"/>
       <c r="J18" s="59"/>
       <c r="K18" s="59"/>
       <c r="L18" s="59"/>
@@ -11750,7 +11749,7 @@
       <c r="H19" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I19" s="81"/>
+      <c r="I19" s="83"/>
       <c r="J19" s="59"/>
       <c r="K19" s="59"/>
       <c r="L19" s="59"/>
@@ -11772,7 +11771,7 @@
       <c r="B20" s="78"/>
       <c r="C20" s="78"/>
       <c r="D20" s="78"/>
-      <c r="E20" s="77" t="s">
+      <c r="E20" s="75" t="s">
         <v>32</v>
       </c>
       <c r="F20" s="58" t="s">
@@ -11782,8 +11781,8 @@
       <c r="H20" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I20" s="86" t="s">
-        <v>53</v>
+      <c r="I20" s="85" t="s">
+        <v>51</v>
       </c>
       <c r="J20" s="59"/>
       <c r="K20" s="59"/>
@@ -11814,7 +11813,7 @@
       <c r="H21" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I21" s="80"/>
+      <c r="I21" s="82"/>
       <c r="J21" s="59"/>
       <c r="K21" s="59"/>
       <c r="L21" s="59"/>
@@ -11844,7 +11843,7 @@
       <c r="H22" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I22" s="80"/>
+      <c r="I22" s="82"/>
       <c r="J22" s="59"/>
       <c r="K22" s="59"/>
       <c r="L22" s="59"/>
@@ -11874,7 +11873,7 @@
       <c r="H23" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I23" s="80"/>
+      <c r="I23" s="82"/>
       <c r="J23" s="59"/>
       <c r="K23" s="59"/>
       <c r="L23" s="59"/>
@@ -11904,7 +11903,7 @@
       <c r="H24" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I24" s="81"/>
+      <c r="I24" s="83"/>
       <c r="J24" s="59"/>
       <c r="K24" s="59"/>
       <c r="L24" s="59"/>
@@ -11939,7 +11938,7 @@
         <v>26</v>
       </c>
       <c r="I25" s="61" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="J25" s="59"/>
       <c r="K25" s="59"/>
@@ -11962,10 +11961,10 @@
       <c r="B26" s="65"/>
       <c r="C26" s="65"/>
       <c r="D26" s="58" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E26" s="58" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F26" s="58" t="s">
         <v>24</v>
@@ -11975,7 +11974,7 @@
         <v>26</v>
       </c>
       <c r="I26" s="58" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="J26" s="59"/>
       <c r="K26" s="59"/>
@@ -12010,10 +12009,10 @@
       <c r="B27" s="65"/>
       <c r="C27" s="65"/>
       <c r="D27" s="58" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E27" s="58" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F27" s="58" t="s">
         <v>24</v>
@@ -12055,29 +12054,29 @@
     </row>
     <row r="28" spans="1:36" ht="15.65" customHeight="1">
       <c r="A28" s="78"/>
-      <c r="B28" s="77" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="77" t="s">
+      <c r="B28" s="75" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="77" t="s">
+      <c r="D28" s="75" t="s">
         <v>22</v>
       </c>
       <c r="E28" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="F28" s="77" t="s">
+      <c r="F28" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="G28" s="77" t="s">
+      <c r="G28" s="75" t="s">
         <v>25</v>
       </c>
       <c r="H28" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I28" s="84" t="s">
-        <v>41</v>
+      <c r="I28" s="81" t="s">
+        <v>39</v>
       </c>
       <c r="J28" s="59"/>
       <c r="K28" s="59"/>
@@ -12108,7 +12107,7 @@
       <c r="H29" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I29" s="80"/>
+      <c r="I29" s="82"/>
       <c r="J29" s="59"/>
       <c r="K29" s="59"/>
       <c r="L29" s="59"/>
@@ -12129,7 +12128,7 @@
       <c r="A30" s="78"/>
       <c r="B30" s="78"/>
       <c r="C30" s="78"/>
-      <c r="D30" s="77" t="s">
+      <c r="D30" s="75" t="s">
         <v>34</v>
       </c>
       <c r="E30" s="58" t="s">
@@ -12140,7 +12139,7 @@
       <c r="H30" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I30" s="80"/>
+      <c r="I30" s="82"/>
       <c r="J30" s="59"/>
       <c r="K30" s="59"/>
       <c r="L30" s="59"/>
@@ -12170,7 +12169,7 @@
       <c r="H31" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I31" s="80"/>
+      <c r="I31" s="82"/>
       <c r="J31" s="59"/>
       <c r="K31" s="59"/>
       <c r="L31" s="59"/>
@@ -12190,10 +12189,10 @@
     <row r="32" spans="1:36" ht="15.65" customHeight="1">
       <c r="A32" s="78"/>
       <c r="B32" s="78"/>
-      <c r="C32" s="77" t="s">
+      <c r="C32" s="75" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="77" t="s">
+      <c r="D32" s="75" t="s">
         <v>22</v>
       </c>
       <c r="E32" s="58" t="s">
@@ -12204,7 +12203,7 @@
       <c r="H32" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I32" s="80"/>
+      <c r="I32" s="82"/>
       <c r="J32" s="59"/>
       <c r="K32" s="59"/>
       <c r="L32" s="59"/>
@@ -12234,7 +12233,7 @@
       <c r="H33" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I33" s="80"/>
+      <c r="I33" s="82"/>
       <c r="J33" s="59"/>
       <c r="K33" s="59"/>
       <c r="L33" s="59"/>
@@ -12266,7 +12265,7 @@
       <c r="H34" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="I34" s="81"/>
+      <c r="I34" s="83"/>
       <c r="J34" s="59"/>
       <c r="K34" s="59"/>
       <c r="L34" s="59"/>
@@ -12285,6 +12284,27 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="C3:C14"/>
+    <mergeCell ref="E8:E12"/>
+    <mergeCell ref="D3:D12"/>
+    <mergeCell ref="I8:I12"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="I3:I7"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="I28:I34"/>
+    <mergeCell ref="G28:G34"/>
+    <mergeCell ref="E15:E19"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="I20:I24"/>
+    <mergeCell ref="F28:F34"/>
+    <mergeCell ref="I15:I19"/>
+    <mergeCell ref="G3:G25"/>
     <mergeCell ref="D32:D33"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="C28:C31"/>
@@ -12300,27 +12320,6 @@
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C15:C25"/>
     <mergeCell ref="B3:B25"/>
-    <mergeCell ref="I28:I34"/>
-    <mergeCell ref="G28:G34"/>
-    <mergeCell ref="E15:E19"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="I20:I24"/>
-    <mergeCell ref="F28:F34"/>
-    <mergeCell ref="I15:I19"/>
-    <mergeCell ref="G3:G25"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="C3:C14"/>
-    <mergeCell ref="E8:E12"/>
-    <mergeCell ref="D3:D12"/>
-    <mergeCell ref="I8:I12"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="I3:I7"/>
-    <mergeCell ref="C1:C2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="R5:T5">
@@ -13101,31 +13100,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15.65" customHeight="1">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="82" t="s">
+      <c r="B1" s="79" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="82" t="s">
+      <c r="C1" s="79" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="82" t="s">
+      <c r="E1" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="75" t="s">
+      <c r="G1" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="75" t="s">
+      <c r="H1" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="96" t="s">
+      <c r="I1" s="93" t="s">
         <v>19</v>
       </c>
       <c r="J1" s="7"/>
@@ -13153,7 +13152,7 @@
       <c r="F2" s="76"/>
       <c r="G2" s="76"/>
       <c r="H2" s="76"/>
-      <c r="I2" s="81"/>
+      <c r="I2" s="83"/>
       <c r="J2" s="57"/>
       <c r="K2" s="57"/>
       <c r="L2" s="57"/>
@@ -13177,7 +13176,7 @@
       <c r="B3" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="94" t="s">
+      <c r="C3" s="96" t="s">
         <v>21</v>
       </c>
       <c r="D3" s="88" t="s">
@@ -13189,14 +13188,14 @@
       <c r="F3" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="G3" s="89" t="s">
         <v>25</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="89" t="s">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="I3" s="97" t="s">
+        <v>41</v>
       </c>
       <c r="J3" s="66"/>
       <c r="K3" s="66"/>
@@ -13223,7 +13222,7 @@
       <c r="F4" s="76"/>
       <c r="G4" s="78"/>
       <c r="H4" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I4" s="78"/>
       <c r="J4" s="66"/>
@@ -13248,12 +13247,12 @@
       <c r="C5" s="91"/>
       <c r="D5" s="78"/>
       <c r="E5" s="78"/>
-      <c r="F5" s="77" t="s">
+      <c r="F5" s="75" t="s">
         <v>28</v>
       </c>
       <c r="G5" s="78"/>
       <c r="H5" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I5" s="78"/>
       <c r="J5" s="66"/>
@@ -13281,7 +13280,7 @@
       <c r="F6" s="76"/>
       <c r="G6" s="78"/>
       <c r="H6" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I6" s="78"/>
       <c r="J6" s="66"/>
@@ -13306,12 +13305,12 @@
       <c r="C7" s="91"/>
       <c r="D7" s="78"/>
       <c r="E7" s="78"/>
-      <c r="F7" s="77" t="s">
+      <c r="F7" s="75" t="s">
         <v>29</v>
       </c>
       <c r="G7" s="78"/>
       <c r="H7" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I7" s="78"/>
       <c r="J7" s="66"/>
@@ -13339,7 +13338,7 @@
       <c r="F8" s="76"/>
       <c r="G8" s="78"/>
       <c r="H8" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I8" s="78"/>
       <c r="J8" s="66"/>
@@ -13364,12 +13363,12 @@
       <c r="C9" s="91"/>
       <c r="D9" s="78"/>
       <c r="E9" s="78"/>
-      <c r="F9" s="77" t="s">
+      <c r="F9" s="75" t="s">
         <v>30</v>
       </c>
       <c r="G9" s="78"/>
       <c r="H9" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I9" s="78"/>
       <c r="J9" s="66"/>
@@ -13397,7 +13396,7 @@
       <c r="F10" s="76"/>
       <c r="G10" s="78"/>
       <c r="H10" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I10" s="78"/>
       <c r="J10" s="66"/>
@@ -13422,12 +13421,12 @@
       <c r="C11" s="91"/>
       <c r="D11" s="78"/>
       <c r="E11" s="78"/>
-      <c r="F11" s="77" t="s">
+      <c r="F11" s="75" t="s">
         <v>31</v>
       </c>
       <c r="G11" s="78"/>
       <c r="H11" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I11" s="78"/>
       <c r="J11" s="66"/>
@@ -13455,7 +13454,7 @@
       <c r="F12" s="76"/>
       <c r="G12" s="78"/>
       <c r="H12" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I12" s="76"/>
       <c r="J12" s="66"/>
@@ -13479,18 +13478,18 @@
       <c r="B13" s="78"/>
       <c r="C13" s="91"/>
       <c r="D13" s="78"/>
-      <c r="E13" s="77" t="s">
+      <c r="E13" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="77" t="s">
+      <c r="F13" s="75" t="s">
         <v>24</v>
       </c>
       <c r="G13" s="78"/>
       <c r="H13" s="67" t="s">
-        <v>42</v>
-      </c>
-      <c r="I13" s="85" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="I13" s="84" t="s">
+        <v>43</v>
       </c>
       <c r="J13" s="66"/>
       <c r="K13" s="66"/>
@@ -13517,7 +13516,7 @@
       <c r="F14" s="76"/>
       <c r="G14" s="78"/>
       <c r="H14" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I14" s="78"/>
       <c r="J14" s="66"/>
@@ -13542,12 +13541,12 @@
       <c r="C15" s="91"/>
       <c r="D15" s="78"/>
       <c r="E15" s="78"/>
-      <c r="F15" s="77" t="s">
+      <c r="F15" s="75" t="s">
         <v>28</v>
       </c>
       <c r="G15" s="78"/>
       <c r="H15" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I15" s="78"/>
       <c r="J15" s="66"/>
@@ -13575,7 +13574,7 @@
       <c r="F16" s="76"/>
       <c r="G16" s="78"/>
       <c r="H16" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I16" s="78"/>
       <c r="J16" s="66"/>
@@ -13600,12 +13599,12 @@
       <c r="C17" s="91"/>
       <c r="D17" s="78"/>
       <c r="E17" s="78"/>
-      <c r="F17" s="77" t="s">
+      <c r="F17" s="75" t="s">
         <v>29</v>
       </c>
       <c r="G17" s="78"/>
       <c r="H17" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I17" s="78"/>
       <c r="J17" s="66"/>
@@ -13633,7 +13632,7 @@
       <c r="F18" s="76"/>
       <c r="G18" s="78"/>
       <c r="H18" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I18" s="78"/>
       <c r="J18" s="66"/>
@@ -13658,12 +13657,12 @@
       <c r="C19" s="91"/>
       <c r="D19" s="78"/>
       <c r="E19" s="78"/>
-      <c r="F19" s="77" t="s">
+      <c r="F19" s="75" t="s">
         <v>30</v>
       </c>
       <c r="G19" s="78"/>
       <c r="H19" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I19" s="78"/>
       <c r="J19" s="66"/>
@@ -13691,7 +13690,7 @@
       <c r="F20" s="76"/>
       <c r="G20" s="78"/>
       <c r="H20" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I20" s="78"/>
       <c r="J20" s="66"/>
@@ -13716,12 +13715,12 @@
       <c r="C21" s="91"/>
       <c r="D21" s="78"/>
       <c r="E21" s="78"/>
-      <c r="F21" s="77" t="s">
+      <c r="F21" s="75" t="s">
         <v>31</v>
       </c>
       <c r="G21" s="78"/>
       <c r="H21" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I21" s="78"/>
       <c r="J21" s="66"/>
@@ -13749,7 +13748,7 @@
       <c r="F22" s="76"/>
       <c r="G22" s="78"/>
       <c r="H22" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I22" s="76"/>
       <c r="J22" s="66"/>
@@ -13772,21 +13771,21 @@
       <c r="A23" s="78"/>
       <c r="B23" s="78"/>
       <c r="C23" s="91"/>
-      <c r="D23" s="87" t="s">
+      <c r="D23" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="77" t="s">
+      <c r="E23" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="F23" s="77" t="s">
+      <c r="F23" s="75" t="s">
         <v>24</v>
       </c>
       <c r="G23" s="78"/>
       <c r="H23" s="67" t="s">
-        <v>42</v>
-      </c>
-      <c r="I23" s="85" t="s">
-        <v>54</v>
+        <v>40</v>
+      </c>
+      <c r="I23" s="84" t="s">
+        <v>52</v>
       </c>
       <c r="J23" s="66"/>
       <c r="K23" s="66"/>
@@ -13813,7 +13812,7 @@
       <c r="F24" s="78"/>
       <c r="G24" s="78"/>
       <c r="H24" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I24" s="78"/>
       <c r="J24" s="66"/>
@@ -13837,13 +13836,13 @@
       <c r="B25" s="78"/>
       <c r="C25" s="91"/>
       <c r="D25" s="78"/>
-      <c r="E25" s="77" t="s">
+      <c r="E25" s="75" t="s">
         <v>32</v>
       </c>
       <c r="F25" s="78"/>
       <c r="G25" s="78"/>
       <c r="H25" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I25" s="78"/>
       <c r="J25" s="66"/>
@@ -13871,7 +13870,7 @@
       <c r="F26" s="76"/>
       <c r="G26" s="78"/>
       <c r="H26" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I26" s="76"/>
       <c r="J26" s="66"/>
@@ -13896,21 +13895,21 @@
       <c r="C27" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="77" t="s">
+      <c r="D27" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="85" t="s">
+      <c r="E27" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="F27" s="77" t="s">
+      <c r="F27" s="75" t="s">
         <v>24</v>
       </c>
       <c r="G27" s="78"/>
       <c r="H27" s="67" t="s">
-        <v>42</v>
-      </c>
-      <c r="I27" s="85" t="s">
-        <v>43</v>
+        <v>40</v>
+      </c>
+      <c r="I27" s="84" t="s">
+        <v>41</v>
       </c>
       <c r="J27" s="66"/>
       <c r="K27" s="66"/>
@@ -13937,7 +13936,7 @@
       <c r="F28" s="76"/>
       <c r="G28" s="78"/>
       <c r="H28" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I28" s="78"/>
       <c r="J28" s="66"/>
@@ -13962,12 +13961,12 @@
       <c r="C29" s="91"/>
       <c r="D29" s="78"/>
       <c r="E29" s="78"/>
-      <c r="F29" s="77" t="s">
+      <c r="F29" s="75" t="s">
         <v>28</v>
       </c>
       <c r="G29" s="78"/>
       <c r="H29" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I29" s="78"/>
       <c r="J29" s="66"/>
@@ -13995,7 +13994,7 @@
       <c r="F30" s="76"/>
       <c r="G30" s="78"/>
       <c r="H30" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I30" s="78"/>
       <c r="J30" s="66"/>
@@ -14020,12 +14019,12 @@
       <c r="C31" s="91"/>
       <c r="D31" s="78"/>
       <c r="E31" s="78"/>
-      <c r="F31" s="77" t="s">
+      <c r="F31" s="75" t="s">
         <v>29</v>
       </c>
       <c r="G31" s="78"/>
       <c r="H31" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I31" s="78"/>
       <c r="J31" s="66"/>
@@ -14053,7 +14052,7 @@
       <c r="F32" s="76"/>
       <c r="G32" s="78"/>
       <c r="H32" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I32" s="78"/>
       <c r="J32" s="66"/>
@@ -14078,12 +14077,12 @@
       <c r="C33" s="91"/>
       <c r="D33" s="78"/>
       <c r="E33" s="78"/>
-      <c r="F33" s="77" t="s">
+      <c r="F33" s="75" t="s">
         <v>30</v>
       </c>
       <c r="G33" s="78"/>
       <c r="H33" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I33" s="78"/>
       <c r="J33" s="66"/>
@@ -14111,7 +14110,7 @@
       <c r="F34" s="76"/>
       <c r="G34" s="78"/>
       <c r="H34" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I34" s="78"/>
       <c r="J34" s="66"/>
@@ -14136,12 +14135,12 @@
       <c r="C35" s="91"/>
       <c r="D35" s="78"/>
       <c r="E35" s="78"/>
-      <c r="F35" s="77" t="s">
+      <c r="F35" s="75" t="s">
         <v>31</v>
       </c>
       <c r="G35" s="78"/>
       <c r="H35" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I35" s="78"/>
       <c r="J35" s="66"/>
@@ -14169,7 +14168,7 @@
       <c r="F36" s="76"/>
       <c r="G36" s="78"/>
       <c r="H36" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I36" s="76"/>
       <c r="J36" s="66"/>
@@ -14193,18 +14192,18 @@
       <c r="B37" s="78"/>
       <c r="C37" s="91"/>
       <c r="D37" s="78"/>
-      <c r="E37" s="77" t="s">
+      <c r="E37" s="75" t="s">
         <v>32</v>
       </c>
-      <c r="F37" s="77" t="s">
+      <c r="F37" s="75" t="s">
         <v>24</v>
       </c>
       <c r="G37" s="78"/>
       <c r="H37" s="67" t="s">
-        <v>42</v>
-      </c>
-      <c r="I37" s="85" t="s">
-        <v>45</v>
+        <v>40</v>
+      </c>
+      <c r="I37" s="84" t="s">
+        <v>43</v>
       </c>
       <c r="J37" s="66"/>
       <c r="K37" s="66"/>
@@ -14231,7 +14230,7 @@
       <c r="F38" s="76"/>
       <c r="G38" s="78"/>
       <c r="H38" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I38" s="78"/>
       <c r="J38" s="66"/>
@@ -14256,12 +14255,12 @@
       <c r="C39" s="91"/>
       <c r="D39" s="78"/>
       <c r="E39" s="78"/>
-      <c r="F39" s="77" t="s">
+      <c r="F39" s="75" t="s">
         <v>28</v>
       </c>
       <c r="G39" s="78"/>
       <c r="H39" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I39" s="78"/>
       <c r="J39" s="66"/>
@@ -14289,7 +14288,7 @@
       <c r="F40" s="76"/>
       <c r="G40" s="78"/>
       <c r="H40" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I40" s="78"/>
       <c r="J40" s="66"/>
@@ -14314,12 +14313,12 @@
       <c r="C41" s="91"/>
       <c r="D41" s="78"/>
       <c r="E41" s="78"/>
-      <c r="F41" s="77" t="s">
+      <c r="F41" s="75" t="s">
         <v>29</v>
       </c>
       <c r="G41" s="78"/>
       <c r="H41" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I41" s="78"/>
       <c r="J41" s="66"/>
@@ -14347,7 +14346,7 @@
       <c r="F42" s="76"/>
       <c r="G42" s="78"/>
       <c r="H42" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I42" s="78"/>
       <c r="J42" s="66"/>
@@ -14372,12 +14371,12 @@
       <c r="C43" s="91"/>
       <c r="D43" s="78"/>
       <c r="E43" s="78"/>
-      <c r="F43" s="77" t="s">
+      <c r="F43" s="75" t="s">
         <v>30</v>
       </c>
       <c r="G43" s="78"/>
       <c r="H43" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I43" s="78"/>
       <c r="J43" s="66"/>
@@ -14405,7 +14404,7 @@
       <c r="F44" s="76"/>
       <c r="G44" s="78"/>
       <c r="H44" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I44" s="78"/>
       <c r="J44" s="66"/>
@@ -14430,12 +14429,12 @@
       <c r="C45" s="91"/>
       <c r="D45" s="78"/>
       <c r="E45" s="78"/>
-      <c r="F45" s="77" t="s">
+      <c r="F45" s="75" t="s">
         <v>31</v>
       </c>
       <c r="G45" s="78"/>
       <c r="H45" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I45" s="78"/>
       <c r="J45" s="66"/>
@@ -14463,7 +14462,7 @@
       <c r="F46" s="76"/>
       <c r="G46" s="78"/>
       <c r="H46" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I46" s="76"/>
       <c r="J46" s="66"/>
@@ -14486,21 +14485,21 @@
       <c r="A47" s="78"/>
       <c r="B47" s="78"/>
       <c r="C47" s="91"/>
-      <c r="D47" s="87" t="s">
+      <c r="D47" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="E47" s="77" t="s">
+      <c r="E47" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="F47" s="87" t="s">
+      <c r="F47" s="80" t="s">
         <v>24</v>
       </c>
       <c r="G47" s="78"/>
       <c r="H47" s="67" t="s">
-        <v>42</v>
-      </c>
-      <c r="I47" s="85" t="s">
-        <v>55</v>
+        <v>40</v>
+      </c>
+      <c r="I47" s="84" t="s">
+        <v>53</v>
       </c>
       <c r="J47" s="66"/>
       <c r="K47" s="66"/>
@@ -14527,7 +14526,7 @@
       <c r="F48" s="78"/>
       <c r="G48" s="78"/>
       <c r="H48" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I48" s="76"/>
       <c r="J48" s="66"/>
@@ -14549,26 +14548,26 @@
     <row r="49" spans="1:24" ht="16.5" customHeight="1">
       <c r="A49" s="78"/>
       <c r="B49" s="78"/>
-      <c r="C49" s="92" t="s">
+      <c r="C49" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="D49" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D49" s="85" t="s">
+      <c r="F49" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="G49" s="75">
+        <v>8</v>
+      </c>
+      <c r="H49" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="I49" s="84" t="s">
         <v>47</v>
-      </c>
-      <c r="E49" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F49" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="G49" s="77">
-        <v>8</v>
-      </c>
-      <c r="H49" s="67" t="s">
-        <v>42</v>
-      </c>
-      <c r="I49" s="85" t="s">
-        <v>49</v>
       </c>
       <c r="J49" s="66"/>
       <c r="K49" s="66"/>
@@ -14592,12 +14591,12 @@
       <c r="C50" s="91"/>
       <c r="D50" s="78"/>
       <c r="E50" s="68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F50" s="76"/>
       <c r="G50" s="78"/>
       <c r="H50" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I50" s="78"/>
       <c r="J50" s="66"/>
@@ -14622,14 +14621,14 @@
       <c r="C51" s="91"/>
       <c r="D51" s="78"/>
       <c r="E51" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F51" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="F51" s="92" t="s">
         <v>28</v>
       </c>
       <c r="G51" s="78"/>
       <c r="H51" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I51" s="78"/>
       <c r="J51" s="66"/>
@@ -14654,12 +14653,12 @@
       <c r="C52" s="91"/>
       <c r="D52" s="76"/>
       <c r="E52" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F52" s="81"/>
+        <v>46</v>
+      </c>
+      <c r="F52" s="83"/>
       <c r="G52" s="76"/>
       <c r="H52" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I52" s="78"/>
       <c r="J52" s="66"/>
@@ -14682,20 +14681,20 @@
       <c r="A53" s="78"/>
       <c r="B53" s="78"/>
       <c r="C53" s="91"/>
-      <c r="D53" s="77" t="s">
-        <v>50</v>
+      <c r="D53" s="75" t="s">
+        <v>48</v>
       </c>
       <c r="E53" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F53" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="F53" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="G53" s="77">
+      <c r="G53" s="75">
         <v>4</v>
       </c>
       <c r="H53" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I53" s="78"/>
       <c r="J53" s="66"/>
@@ -14720,12 +14719,12 @@
       <c r="C54" s="91"/>
       <c r="D54" s="78"/>
       <c r="E54" s="68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F54" s="76"/>
       <c r="G54" s="78"/>
       <c r="H54" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I54" s="78"/>
       <c r="J54" s="66"/>
@@ -14750,14 +14749,14 @@
       <c r="C55" s="91"/>
       <c r="D55" s="78"/>
       <c r="E55" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F55" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="F55" s="75" t="s">
         <v>30</v>
       </c>
       <c r="G55" s="78"/>
       <c r="H55" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I55" s="78"/>
       <c r="J55" s="66"/>
@@ -14782,12 +14781,12 @@
       <c r="C56" s="91"/>
       <c r="D56" s="78"/>
       <c r="E56" s="68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F56" s="76"/>
       <c r="G56" s="76"/>
       <c r="H56" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I56" s="78"/>
       <c r="J56" s="66"/>
@@ -14812,16 +14811,16 @@
       <c r="C57" s="91"/>
       <c r="D57" s="78"/>
       <c r="E57" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F57" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="F57" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="G57" s="77">
+      <c r="G57" s="75">
         <v>1</v>
       </c>
       <c r="H57" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I57" s="78"/>
       <c r="J57" s="66"/>
@@ -14846,12 +14845,12 @@
       <c r="C58" s="91"/>
       <c r="D58" s="76"/>
       <c r="E58" s="68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F58" s="76"/>
       <c r="G58" s="76"/>
       <c r="H58" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I58" s="78"/>
       <c r="J58" s="66"/>
@@ -14874,20 +14873,20 @@
       <c r="A59" s="78"/>
       <c r="B59" s="78"/>
       <c r="C59" s="91"/>
-      <c r="D59" s="77" t="s">
+      <c r="D59" s="75" t="s">
         <v>34</v>
       </c>
       <c r="E59" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F59" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="F59" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="G59" s="77">
+      <c r="G59" s="75">
         <v>8</v>
       </c>
       <c r="H59" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I59" s="78"/>
       <c r="J59" s="66"/>
@@ -14909,15 +14908,15 @@
     <row r="60" spans="1:24" ht="16.5" customHeight="1">
       <c r="A60" s="78"/>
       <c r="B60" s="76"/>
-      <c r="C60" s="93"/>
+      <c r="C60" s="95"/>
       <c r="D60" s="76"/>
       <c r="E60" s="68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F60" s="76"/>
       <c r="G60" s="76"/>
       <c r="H60" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I60" s="76"/>
       <c r="J60" s="66"/>
@@ -14938,29 +14937,29 @@
     </row>
     <row r="61" spans="1:24" ht="16.5" customHeight="1">
       <c r="A61" s="78"/>
-      <c r="B61" s="77" t="s">
-        <v>40</v>
+      <c r="B61" s="75" t="s">
+        <v>38</v>
       </c>
       <c r="C61" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D61" s="87" t="s">
+      <c r="D61" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="E61" s="87" t="s">
+      <c r="E61" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="F61" s="87" t="s">
+      <c r="F61" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="G61" s="87" t="s">
+      <c r="G61" s="80" t="s">
         <v>25</v>
       </c>
       <c r="H61" s="67" t="s">
-        <v>42</v>
-      </c>
-      <c r="I61" s="85" t="s">
-        <v>51</v>
+        <v>40</v>
+      </c>
+      <c r="I61" s="84" t="s">
+        <v>49</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -14987,7 +14986,7 @@
       <c r="F62" s="78"/>
       <c r="G62" s="78"/>
       <c r="H62" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I62" s="78"/>
       <c r="J62" s="66"/>
@@ -15011,13 +15010,13 @@
       <c r="B63" s="78"/>
       <c r="C63" s="91"/>
       <c r="D63" s="78"/>
-      <c r="E63" s="87" t="s">
+      <c r="E63" s="80" t="s">
         <v>32</v>
       </c>
       <c r="F63" s="78"/>
       <c r="G63" s="78"/>
       <c r="H63" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I63" s="78"/>
       <c r="J63" s="66"/>
@@ -15045,7 +15044,7 @@
       <c r="F64" s="78"/>
       <c r="G64" s="78"/>
       <c r="H64" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I64" s="78"/>
       <c r="J64" s="66"/>
@@ -15068,16 +15067,16 @@
       <c r="A65" s="78"/>
       <c r="B65" s="78"/>
       <c r="C65" s="91"/>
-      <c r="D65" s="87" t="s">
+      <c r="D65" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="E65" s="77" t="s">
+      <c r="E65" s="75" t="s">
         <v>23</v>
       </c>
       <c r="F65" s="78"/>
       <c r="G65" s="78"/>
       <c r="H65" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I65" s="78"/>
       <c r="J65" s="66"/>
@@ -15105,7 +15104,7 @@
       <c r="F66" s="78"/>
       <c r="G66" s="78"/>
       <c r="H66" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I66" s="78"/>
       <c r="J66" s="66"/>
@@ -15129,13 +15128,13 @@
       <c r="B67" s="78"/>
       <c r="C67" s="91"/>
       <c r="D67" s="78"/>
-      <c r="E67" s="77" t="s">
+      <c r="E67" s="75" t="s">
         <v>32</v>
       </c>
       <c r="F67" s="78"/>
       <c r="G67" s="78"/>
       <c r="H67" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I67" s="78"/>
       <c r="J67" s="66"/>
@@ -15163,7 +15162,7 @@
       <c r="F68" s="78"/>
       <c r="G68" s="78"/>
       <c r="H68" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I68" s="78"/>
       <c r="J68" s="66"/>
@@ -15188,16 +15187,16 @@
       <c r="C69" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="D69" s="87" t="s">
+      <c r="D69" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="E69" s="87" t="s">
+      <c r="E69" s="80" t="s">
         <v>23</v>
       </c>
       <c r="F69" s="78"/>
       <c r="G69" s="78"/>
       <c r="H69" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I69" s="78"/>
       <c r="J69" s="66"/>
@@ -15225,7 +15224,7 @@
       <c r="F70" s="78"/>
       <c r="G70" s="78"/>
       <c r="H70" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I70" s="78"/>
       <c r="J70" s="66"/>
@@ -15249,13 +15248,13 @@
       <c r="B71" s="78"/>
       <c r="C71" s="91"/>
       <c r="D71" s="78"/>
-      <c r="E71" s="87" t="s">
+      <c r="E71" s="80" t="s">
         <v>32</v>
       </c>
       <c r="F71" s="78"/>
       <c r="G71" s="78"/>
       <c r="H71" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I71" s="78"/>
       <c r="J71" s="66"/>
@@ -15283,7 +15282,7 @@
       <c r="F72" s="78"/>
       <c r="G72" s="78"/>
       <c r="H72" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I72" s="78"/>
       <c r="J72" s="66"/>
@@ -15306,16 +15305,16 @@
       <c r="A73" s="78"/>
       <c r="B73" s="78"/>
       <c r="C73" s="91"/>
-      <c r="D73" s="87" t="s">
+      <c r="D73" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="E73" s="77" t="s">
+      <c r="E73" s="75" t="s">
         <v>23</v>
       </c>
       <c r="F73" s="78"/>
       <c r="G73" s="78"/>
       <c r="H73" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I73" s="78"/>
       <c r="J73" s="66"/>
@@ -15343,7 +15342,7 @@
       <c r="F74" s="78"/>
       <c r="G74" s="78"/>
       <c r="H74" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I74" s="76"/>
       <c r="J74" s="66"/>
@@ -15365,26 +15364,26 @@
     <row r="75" spans="1:24" ht="16.5" customHeight="1">
       <c r="A75" s="78"/>
       <c r="B75" s="78"/>
-      <c r="C75" s="92" t="s">
+      <c r="C75" s="94" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" s="84" t="s">
+        <v>45</v>
+      </c>
+      <c r="E75" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="D75" s="85" t="s">
+      <c r="F75" s="75" t="s">
+        <v>24</v>
+      </c>
+      <c r="G75" s="75">
+        <v>8</v>
+      </c>
+      <c r="H75" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="I75" s="84" t="s">
         <v>47</v>
-      </c>
-      <c r="E75" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F75" s="77" t="s">
-        <v>24</v>
-      </c>
-      <c r="G75" s="77">
-        <v>8</v>
-      </c>
-      <c r="H75" s="67" t="s">
-        <v>42</v>
-      </c>
-      <c r="I75" s="85" t="s">
-        <v>49</v>
       </c>
       <c r="J75" s="66"/>
       <c r="K75" s="66"/>
@@ -15408,12 +15407,12 @@
       <c r="C76" s="91"/>
       <c r="D76" s="78"/>
       <c r="E76" s="68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F76" s="76"/>
       <c r="G76" s="78"/>
       <c r="H76" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I76" s="78"/>
       <c r="J76" s="66"/>
@@ -15438,14 +15437,14 @@
       <c r="C77" s="91"/>
       <c r="D77" s="78"/>
       <c r="E77" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F77" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="F77" s="92" t="s">
         <v>28</v>
       </c>
       <c r="G77" s="78"/>
       <c r="H77" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I77" s="78"/>
       <c r="J77" s="66"/>
@@ -15470,12 +15469,12 @@
       <c r="C78" s="91"/>
       <c r="D78" s="76"/>
       <c r="E78" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F78" s="81"/>
+        <v>46</v>
+      </c>
+      <c r="F78" s="83"/>
       <c r="G78" s="76"/>
       <c r="H78" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I78" s="78"/>
       <c r="J78" s="66"/>
@@ -15498,20 +15497,20 @@
       <c r="A79" s="78"/>
       <c r="B79" s="78"/>
       <c r="C79" s="91"/>
-      <c r="D79" s="77" t="s">
-        <v>50</v>
+      <c r="D79" s="75" t="s">
+        <v>48</v>
       </c>
       <c r="E79" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F79" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="F79" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="G79" s="77">
+      <c r="G79" s="75">
         <v>4</v>
       </c>
       <c r="H79" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I79" s="78"/>
       <c r="J79" s="66"/>
@@ -15536,12 +15535,12 @@
       <c r="C80" s="91"/>
       <c r="D80" s="78"/>
       <c r="E80" s="68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F80" s="76"/>
       <c r="G80" s="78"/>
       <c r="H80" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I80" s="78"/>
       <c r="J80" s="66"/>
@@ -15566,14 +15565,14 @@
       <c r="C81" s="91"/>
       <c r="D81" s="78"/>
       <c r="E81" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F81" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="F81" s="75" t="s">
         <v>30</v>
       </c>
       <c r="G81" s="78"/>
       <c r="H81" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I81" s="78"/>
       <c r="J81" s="66"/>
@@ -15598,12 +15597,12 @@
       <c r="C82" s="91"/>
       <c r="D82" s="78"/>
       <c r="E82" s="68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F82" s="76"/>
       <c r="G82" s="76"/>
       <c r="H82" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I82" s="78"/>
       <c r="J82" s="66"/>
@@ -15628,16 +15627,16 @@
       <c r="C83" s="91"/>
       <c r="D83" s="78"/>
       <c r="E83" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F83" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="F83" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="G83" s="77">
+      <c r="G83" s="75">
         <v>1</v>
       </c>
       <c r="H83" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I83" s="78"/>
       <c r="J83" s="66"/>
@@ -15662,12 +15661,12 @@
       <c r="C84" s="91"/>
       <c r="D84" s="76"/>
       <c r="E84" s="68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F84" s="76"/>
       <c r="G84" s="76"/>
       <c r="H84" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I84" s="78"/>
       <c r="J84" s="66"/>
@@ -15690,20 +15689,20 @@
       <c r="A85" s="78"/>
       <c r="B85" s="78"/>
       <c r="C85" s="91"/>
-      <c r="D85" s="77" t="s">
+      <c r="D85" s="75" t="s">
         <v>34</v>
       </c>
       <c r="E85" s="68" t="s">
-        <v>48</v>
-      </c>
-      <c r="F85" s="77" t="s">
+        <v>46</v>
+      </c>
+      <c r="F85" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="G85" s="77">
+      <c r="G85" s="75">
         <v>8</v>
       </c>
       <c r="H85" s="67" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I85" s="78"/>
       <c r="J85" s="66"/>
@@ -15725,15 +15724,15 @@
     <row r="86" spans="1:24" ht="16.5" customHeight="1">
       <c r="A86" s="76"/>
       <c r="B86" s="76"/>
-      <c r="C86" s="93"/>
+      <c r="C86" s="95"/>
       <c r="D86" s="76"/>
       <c r="E86" s="68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F86" s="76"/>
       <c r="G86" s="76"/>
       <c r="H86" s="67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I86" s="76"/>
       <c r="J86" s="66"/>
@@ -15754,6 +15753,90 @@
     </row>
   </sheetData>
   <mergeCells count="100">
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="D61:D64"/>
+    <mergeCell ref="F75:F76"/>
+    <mergeCell ref="I23:I26"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="F41:F42"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="I27:I36"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="I75:I86"/>
+    <mergeCell ref="E3:E12"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="F59:F60"/>
+    <mergeCell ref="I3:I12"/>
+    <mergeCell ref="I49:I60"/>
+    <mergeCell ref="G85:G86"/>
+    <mergeCell ref="F43:F44"/>
+    <mergeCell ref="C61:C68"/>
+    <mergeCell ref="G61:G74"/>
+    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="D85:D86"/>
+    <mergeCell ref="F79:F80"/>
+    <mergeCell ref="F81:F82"/>
+    <mergeCell ref="F83:F84"/>
+    <mergeCell ref="G79:G82"/>
+    <mergeCell ref="C75:C86"/>
+    <mergeCell ref="D75:D78"/>
+    <mergeCell ref="D79:D84"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="E73:E74"/>
+    <mergeCell ref="C3:C26"/>
+    <mergeCell ref="F77:F78"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="E61:E62"/>
+    <mergeCell ref="G75:G78"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="E37:E46"/>
+    <mergeCell ref="E13:E22"/>
+    <mergeCell ref="C69:C74"/>
+    <mergeCell ref="F45:F46"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="D27:D46"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="I37:I46"/>
+    <mergeCell ref="F49:F50"/>
+    <mergeCell ref="I13:I22"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="E27:E36"/>
+    <mergeCell ref="B3:B60"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="D49:D52"/>
+    <mergeCell ref="F51:F52"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="C49:C60"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G53:G56"/>
+    <mergeCell ref="A3:A86"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="D23:D26"/>
+    <mergeCell ref="E67:E68"/>
+    <mergeCell ref="E71:E72"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="F55:F56"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="D65:D68"/>
+    <mergeCell ref="F23:F26"/>
+    <mergeCell ref="E65:E66"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="F61:F74"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="D73:D74"/>
+    <mergeCell ref="I61:I74"/>
     <mergeCell ref="B61:B86"/>
     <mergeCell ref="F85:F86"/>
     <mergeCell ref="D3:D22"/>
@@ -15770,90 +15853,6 @@
     <mergeCell ref="C27:C48"/>
     <mergeCell ref="D47:D48"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="F61:F74"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="D73:D74"/>
-    <mergeCell ref="I61:I74"/>
-    <mergeCell ref="A3:A86"/>
-    <mergeCell ref="F57:F58"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="D23:D26"/>
-    <mergeCell ref="E67:E68"/>
-    <mergeCell ref="E71:E72"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="F55:F56"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="D65:D68"/>
-    <mergeCell ref="F23:F26"/>
-    <mergeCell ref="E65:E66"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="I37:I46"/>
-    <mergeCell ref="F49:F50"/>
-    <mergeCell ref="I13:I22"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="E27:E36"/>
-    <mergeCell ref="B3:B60"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="D49:D52"/>
-    <mergeCell ref="F51:F52"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="C49:C60"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G53:G56"/>
-    <mergeCell ref="C3:C26"/>
-    <mergeCell ref="F77:F78"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="E61:E62"/>
-    <mergeCell ref="G75:G78"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="E37:E46"/>
-    <mergeCell ref="E13:E22"/>
-    <mergeCell ref="C69:C74"/>
-    <mergeCell ref="F45:F46"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="D27:D46"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="G85:G86"/>
-    <mergeCell ref="F43:F44"/>
-    <mergeCell ref="C61:C68"/>
-    <mergeCell ref="G61:G74"/>
-    <mergeCell ref="F53:F54"/>
-    <mergeCell ref="D85:D86"/>
-    <mergeCell ref="F79:F80"/>
-    <mergeCell ref="F81:F82"/>
-    <mergeCell ref="F83:F84"/>
-    <mergeCell ref="G79:G82"/>
-    <mergeCell ref="C75:C86"/>
-    <mergeCell ref="D75:D78"/>
-    <mergeCell ref="D79:D84"/>
-    <mergeCell ref="G83:G84"/>
-    <mergeCell ref="E73:E74"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="D61:D64"/>
-    <mergeCell ref="F75:F76"/>
-    <mergeCell ref="I23:I26"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="F41:F42"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="I27:I36"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="I75:I86"/>
-    <mergeCell ref="E3:E12"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="F59:F60"/>
-    <mergeCell ref="I3:I12"/>
-    <mergeCell ref="I49:I60"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="J3:X3">
